--- a/src/New-release-old/Figure7.xlsx
+++ b/src/New-release-old/Figure7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officenationalstatistics.sharepoint.com/sites/msdfp/fp/FLOVERVIEW/Floverview + LCLI 2025 IndQ2 - 2025 WEQ3/Figures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\visualisations\dvc3400-3499\dvc3488-productivity-flash\fig7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5562CA3-828E-4E9B-89F4-1165ABD100D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DD1E398-D4D9-404B-86A0-4844A7FC7F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data for Dataviz" sheetId="2" r:id="rId1"/>
@@ -38,10 +38,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
-    <t>Figure 7: In 2025Q2 the IT industry saw output per hour grow by 36.7% in comparison with its 2019 average due to a large increase in GVA (up from 29.2% a quarter ago and before Bluebook 25 revisions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decomposition of growth of output per hour worked, hours worked and gross value added (GVA), Quarter 2 (Apr to Jun) 2025 compared with 2019 average, percentage change, UK </t>
+    <t>Figure 7: Output per hour in the IT industry grew by 32%, compared with its 2019 average, because of a large increase in gross value added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decomposition of growth of output per hour worked, hours worked and gross value added (GVA), Quarter 3 (Jul to Sep) 2025 compared with 2019 average, percentage change, UK </t>
   </si>
   <si>
     <t>Notes</t>
@@ -59,7 +59,7 @@
     <t>GVA</t>
   </si>
   <si>
-    <t>Hours worked (sign reversed)</t>
+    <t>Hours worked</t>
   </si>
   <si>
     <t>Output per hour worked</t>
@@ -129,17 +129,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -168,10 +164,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -509,31 +504,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F044E81-6507-406E-A706-F956F5590C89}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -541,7 +536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -555,329 +550,329 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="3">
-        <v>5.8260935201601E-2</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3.49609718051338E-2</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2.25128908540661E-2</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="B8" s="2">
+        <v>5.8249889078513896E-2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2.8929548994404797E-2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2.8495964677819299E-2</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="3">
-        <v>5.0226191857093198E-2</v>
-      </c>
-      <c r="C9" s="3">
-        <v>-0.13596610053049299</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.215491883480386</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="B9" s="2">
+        <v>5.7185941306112806E-2</v>
+      </c>
+      <c r="C9" s="2">
+        <v>-0.13585731409433099</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.22339280138455903</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="3">
-        <v>-0.39293214406683902</v>
-      </c>
-      <c r="C10" s="3">
-        <v>-0.25321468064623004</v>
-      </c>
-      <c r="D10" s="3">
-        <v>-0.18709187205435801</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="B10" s="2">
+        <v>-0.38471265665575205</v>
+      </c>
+      <c r="C10" s="2">
+        <v>-0.138518313667438</v>
+      </c>
+      <c r="D10" s="2">
+        <v>-0.285780123819456</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3">
-        <v>4.2571024223576802E-2</v>
-      </c>
-      <c r="C11" s="3">
-        <v>-4.7980577264259396E-2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>9.5115287908334512E-2</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="B11" s="2">
+        <v>4.6363257473401601E-2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-7.5203179315919091E-2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.131452048785588</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="3">
-        <v>-0.50822046631284201</v>
-      </c>
-      <c r="C12" s="3">
-        <v>4.06417606487008E-2</v>
-      </c>
-      <c r="D12" s="3">
-        <v>-0.52742667814849298</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="B12" s="2">
+        <v>-0.496503194145687</v>
+      </c>
+      <c r="C12" s="2">
+        <v>6.2502992684060302E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>-0.52612198805916299</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="3">
-        <v>0.16135272889616398</v>
-      </c>
-      <c r="C13" s="3">
-        <v>0.13211100356955399</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2.5829380011686397E-2</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="B13" s="2">
+        <v>0.159864578295323</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.11732006264510501</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3.8077286063851599E-2</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="3">
-        <v>4.2653898204950205E-2</v>
-      </c>
-      <c r="C14" s="3">
-        <v>-5.21275025686933E-2</v>
-      </c>
-      <c r="D14" s="3">
-        <v>9.9993829371035792E-2</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="B14" s="2">
+        <v>4.3753048424436801E-2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-1.2763024621408301E-2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>5.7246714269562494E-2</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="3">
-        <v>-8.1484893625715496E-2</v>
-      </c>
-      <c r="C15" s="3">
-        <v>-5.5969414178603197E-2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>-2.7028233862689398E-2</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="B15" s="2">
+        <v>-8.3698934956963594E-2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>-6.9575341574596605E-2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>-1.5179728153668E-2</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="3">
-        <v>8.0414907331842894E-2</v>
-      </c>
-      <c r="C16" s="3">
-        <v>-4.8679133106332897E-3</v>
-      </c>
-      <c r="D16" s="3">
-        <v>8.5700000817175506E-2</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="B16" s="2">
+        <v>6.3099504429384001E-2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3.5865604306277699E-3</v>
+      </c>
+      <c r="D16" s="2">
+        <v>5.9300260032597495E-2</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="3">
-        <v>-2.8151510239368901E-2</v>
-      </c>
-      <c r="C17" s="3">
-        <v>6.1796114375139703E-2</v>
-      </c>
-      <c r="D17" s="3">
-        <v>-8.4712708397357395E-2</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="B17" s="2">
+        <v>-3.4527476090128004E-2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1.12631481173579E-2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>-4.5280621856668105E-2</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="3">
-        <v>0.43293044701734096</v>
-      </c>
-      <c r="C18" s="3">
-        <v>4.8059584097887402E-2</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0.36722231136384204</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="B18" s="2">
+        <v>0.41109660795714603</v>
+      </c>
+      <c r="C18" s="2">
+        <v>6.9070132195539508E-2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.31992894148037698</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="3">
-        <v>-8.92960356707065E-2</v>
-      </c>
-      <c r="C19" s="3">
-        <v>5.3733888854991196E-2</v>
-      </c>
-      <c r="D19" s="3">
-        <v>-0.13573628601915499</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="B19" s="2">
+        <v>-8.2818793177793795E-2</v>
+      </c>
+      <c r="C19" s="2">
+        <v>4.4803029975622098E-2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>-0.122149170218613</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="3">
-        <v>5.39905826262434E-2</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0.202723913506234</v>
-      </c>
-      <c r="D20" s="3">
-        <v>-0.123663734635821</v>
-      </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="B20" s="2">
+        <v>6.0504856202131301E-2</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.2123980669146</v>
+      </c>
+      <c r="D20" s="2">
+        <v>-0.125283283483796</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="3">
-        <v>0.26949149672343004</v>
-      </c>
-      <c r="C21" s="3">
-        <v>9.1796281643981903E-2</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0.16275491872154199</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="B21" s="2">
+        <v>0.27147832271246902</v>
+      </c>
+      <c r="C21" s="2">
+        <v>8.8277027854151993E-2</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.16834067996413601</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="3">
-        <v>0.11338613096387799</v>
-      </c>
-      <c r="C22" s="3">
-        <v>-5.4190543865861797E-4</v>
-      </c>
-      <c r="D22" s="3">
-        <v>0.11398980809949701</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="B22" s="2">
+        <v>0.113218163952599</v>
+      </c>
+      <c r="C22" s="2">
+        <v>-1.5186752757442501E-2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.130385042107802</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="3">
-        <v>0.16350152297708898</v>
-      </c>
-      <c r="C23" s="3">
-        <v>0.15943894038348799</v>
-      </c>
-      <c r="D23" s="3">
-        <v>3.50392112262265E-3</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="B23" s="2">
+        <v>0.17017613561117698</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.16999752575847499</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1.5265831659427799E-4</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="3">
-        <v>4.1618075280279901E-2</v>
-      </c>
-      <c r="C24" s="3">
-        <v>4.5041388189657999E-2</v>
-      </c>
-      <c r="D24" s="3">
-        <v>-3.27576778112925E-3</v>
-      </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="B24" s="2">
+        <v>4.6368703092916297E-2</v>
+      </c>
+      <c r="C24" s="2">
+        <v>6.0078750976112899E-2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>-1.2933046597314299E-2</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="3">
-        <v>4.4756900061544203E-2</v>
-      </c>
-      <c r="C25" s="3">
-        <v>0.17448093591650299</v>
-      </c>
-      <c r="D25" s="3">
-        <v>-0.11045222777816199</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="B25" s="2">
+        <v>4.1727027410879101E-2</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.16027883730341799</v>
+      </c>
+      <c r="D25" s="2">
+        <v>-0.102175275529512</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="3">
-        <v>1.1811139583517401E-2</v>
-      </c>
-      <c r="C26" s="3">
-        <v>0.10753261320610999</v>
-      </c>
-      <c r="D26" s="3">
-        <v>-8.6427679403044314E-2</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="B26" s="2">
+        <v>3.4196341786692598E-2</v>
+      </c>
+      <c r="C26" s="2">
+        <v>5.3557231261418294E-2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>-1.8376685100955501E-2</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="3">
-        <v>-3.5229071663161901E-2</v>
-      </c>
-      <c r="C27" s="3">
-        <v>4.0404630917779599E-2</v>
-      </c>
-      <c r="D27" s="3">
-        <v>-7.2696430151624997E-2</v>
-      </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
+      <c r="B27" s="2">
+        <v>-6.5094629397726991E-2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2.17895372542962E-2</v>
+      </c>
+      <c r="D27" s="2">
+        <v>-8.5031372395429003E-2</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -886,19 +881,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0CEF6E26CBF2C4F8000DAAA032CD586" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3825d4c36eddbd19ff5877cf568b1130">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a54c791-04d1-4dd7-97a3-a882d4048403" xmlns:ns3="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20db92a579f18a3b40827b4b7272a8b7" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0CEF6E26CBF2C4F8000DAAA032CD586" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7387ef7178ec9fe6b285910e58c20d0b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a54c791-04d1-4dd7-97a3-a882d4048403" xmlns:ns3="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fee36ab1686691439382caeb7e5f0351" ns2:_="" ns3:_="">
     <xsd:import namespace="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
     <xsd:import namespace="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
     <xsd:element name="properties">
@@ -1145,6 +1129,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1155,13 +1150,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DA9672E-0F58-416B-8B3A-FA7330BAA036}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD18BD6C-5E00-4920-98BC-7E7255DB54D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
+    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8C77810-B834-48E6-BFAF-4A4D27671E71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DA9672E-0F58-416B-8B3A-FA7330BAA036}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
+    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF1937A-CB3E-495A-B59F-005F61E111B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF1937A-CB3E-495A-B59F-005F61E111B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>